--- a/artfynd/A 31894-2022 artfynd.xlsx
+++ b/artfynd/A 31894-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31894-2022 artfynd.xlsx
+++ b/artfynd/A 31894-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111733255</v>
+        <v>120098035</v>
       </c>
       <c r="B2" t="n">
-        <v>86145</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4374</v>
+        <v>245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gul vaxskivling</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrocybe chlorophana</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Wünsche</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundstorp Ö, Ög</t>
+          <t>Sundstorp Ö, Hävla, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549104</v>
+        <v>549081</v>
       </c>
       <c r="R2" t="n">
-        <v>6531856</v>
+        <v>6531914</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111733276</v>
+        <v>113071881</v>
       </c>
       <c r="B3" t="n">
-        <v>86161</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4383</v>
+        <v>1008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Småvaxskivling</t>
+          <t>Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrocybe insipida</t>
+          <t>Lycoperdon echinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(J.E.Lange) M.M.Moser</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,14 +815,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundstorp Ö, Ög</t>
+          <t>Sundstorp, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549104</v>
+        <v>548974</v>
       </c>
       <c r="R3" t="n">
-        <v>6531856</v>
+        <v>6531870</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,12 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113071881</v>
+        <v>111733255</v>
       </c>
       <c r="B4" t="n">
-        <v>87524</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1008</v>
+        <v>4374</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Igelkottsröksvamp</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycoperdon echinatum</t>
+          <t>Hygrocybe chlorophana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Fr.) Wünsche</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -926,14 +916,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundstorp, Ög</t>
+          <t>Sundstorp Ö, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548974</v>
+        <v>549105</v>
       </c>
       <c r="R4" t="n">
-        <v>6531870</v>
+        <v>6531857</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,12 +950,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113071867</v>
+        <v>111733276</v>
       </c>
       <c r="B5" t="n">
-        <v>86825</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +994,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4394</v>
+        <v>4383</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Honungsvaxskivling</t>
+          <t>Småvaxing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Hygrocybe insipida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(J.E.Lange) M.M.Moser</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549117</v>
+        <v>549105</v>
       </c>
       <c r="R5" t="n">
-        <v>6531853</v>
+        <v>6531857</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,15 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116982827</v>
+        <v>113071867</v>
       </c>
       <c r="B6" t="n">
-        <v>56199</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,46 +1095,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>4394</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sundstorp, Hävla, Ög</t>
+          <t>Sundstorp Ö, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549012</v>
+        <v>549118</v>
       </c>
       <c r="R6" t="n">
-        <v>6531857</v>
+        <v>6531853</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,12 +1152,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,6 +1166,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1213,12 +1188,7 @@
         <v>116982832</v>
       </c>
       <c r="B7" t="n">
-        <v>56194</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,37 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116982834</v>
+        <v>116982827</v>
       </c>
       <c r="B8" t="n">
-        <v>56180</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1430,6 +1395,338 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>116982834</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sundstorp, Hävla, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>549012</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6531857</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123873636</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sundstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>548977</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6531892</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>Erik Zachariassen</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126172122</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ängsstugorna, Hävla, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>548857</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6531511</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31894-2022 artfynd.xlsx
+++ b/artfynd/A 31894-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,37 +781,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113071881</v>
+        <v>135435136</v>
       </c>
       <c r="B3" t="n">
-        <v>88424</v>
+        <v>107789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1008</v>
+        <v>245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Igelkottsröksvamp</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycoperdon echinatum</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -819,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548974</v>
+        <v>549069</v>
       </c>
       <c r="R3" t="n">
-        <v>6531870</v>
+        <v>6531917</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,12 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111733255</v>
+        <v>113071881</v>
       </c>
       <c r="B4" t="n">
-        <v>89081</v>
+        <v>88424</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4374</v>
+        <v>1008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulvaxing</t>
+          <t>Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrocybe chlorophana</t>
+          <t>Lycoperdon echinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Wünsche</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -916,14 +929,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundstorp Ö, Ög</t>
+          <t>Sundstorp, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549105</v>
+        <v>548974</v>
       </c>
       <c r="R4" t="n">
-        <v>6531857</v>
+        <v>6531870</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111733276</v>
+        <v>111733255</v>
       </c>
       <c r="B5" t="n">
-        <v>89096</v>
+        <v>89081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -994,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4383</v>
+        <v>4374</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Småvaxing</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrocybe insipida</t>
+          <t>Hygrocybe chlorophana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(J.E.Lange) M.M.Moser</t>
+          <t>(Fr.) Wünsche</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113071867</v>
+        <v>111733276</v>
       </c>
       <c r="B6" t="n">
-        <v>89106</v>
+        <v>89096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4394</v>
+        <v>4383</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Småvaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Hygrocybe insipida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(J.E.Lange) M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1122,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549118</v>
+        <v>549105</v>
       </c>
       <c r="R6" t="n">
-        <v>6531853</v>
+        <v>6531857</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,12 +1165,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116982832</v>
+        <v>113071867</v>
       </c>
       <c r="B7" t="n">
-        <v>56830</v>
+        <v>89106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,46 +1209,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100092</v>
+        <v>4394</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundstorp, Hävla, Ög</t>
+          <t>Sundstorp Ö, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549012</v>
+        <v>549118</v>
       </c>
       <c r="R7" t="n">
-        <v>6531857</v>
+        <v>6531853</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1259,12 +1266,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1273,6 +1280,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1291,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116982827</v>
+        <v>116982832</v>
       </c>
       <c r="B8" t="n">
-        <v>56835</v>
+        <v>56830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,21 +1310,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,32 +1405,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116982834</v>
+        <v>116982827</v>
       </c>
       <c r="B9" t="n">
-        <v>56816</v>
+        <v>56835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,61 +1511,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123873636</v>
+        <v>116982834</v>
       </c>
       <c r="B10" t="n">
-        <v>58815</v>
+        <v>56816</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208250</v>
+        <v>205998</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sundstorp, Ög</t>
+          <t>Sundstorp, Hävla, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548977</v>
+        <v>549012</v>
       </c>
       <c r="R10" t="n">
-        <v>6531892</v>
+        <v>6531857</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,12 +1585,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,16 +1599,10 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>Erik Zachariassen</t>
-        </is>
-      </c>
       <c r="AW10" t="inlineStr">
         <is>
           <t>Caspar Ström</t>
@@ -1619,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126172122</v>
+        <v>123873636</v>
       </c>
       <c r="B11" t="n">
-        <v>99155</v>
+        <v>58815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1630,49 +1628,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223621</v>
+        <v>208250</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ängsstugorna, Hävla, Ög</t>
+          <t>Sundstorp, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548857</v>
+        <v>548977</v>
       </c>
       <c r="R11" t="n">
-        <v>6531511</v>
+        <v>6531892</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1696,12 +1695,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,6 +1714,11 @@
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>Erik Zachariassen</t>
+        </is>
+      </c>
       <c r="AW11" t="inlineStr">
         <is>
           <t>Caspar Ström</t>
@@ -1726,6 +1730,116 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126172122</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ängsstugorna, Hävla, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>548857</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6531511</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31894-2022 artfynd.xlsx
+++ b/artfynd/A 31894-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120098035</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135435136</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113071881</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111733255</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111733276</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113071867</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116982832</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116982827</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1614,6 +1659,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116982834</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1730,6 +1780,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123873636</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1840,8 +1895,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126172122</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31894-2022 artfynd.xlsx
+++ b/artfynd/A 31894-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135435136</v>
       </c>
       <c r="B3" t="n">
-        <v>107789</v>
+        <v>107844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31894-2022 artfynd.xlsx
+++ b/artfynd/A 31894-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135435136</v>
       </c>
       <c r="B3" t="n">
-        <v>107844</v>
+        <v>107871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31894-2022 artfynd.xlsx
+++ b/artfynd/A 31894-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,37 +791,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113071881</v>
+        <v>135435136</v>
       </c>
       <c r="B3" t="n">
-        <v>88424</v>
+        <v>107876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1008</v>
+        <v>245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Igelkottsröksvamp</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycoperdon echinatum</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548974</v>
+        <v>549069</v>
       </c>
       <c r="R3" t="n">
-        <v>6531870</v>
+        <v>6531917</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,12 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,16 +904,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113071881</t>
+          <t>https://artportalen.se/Sighting/135435136</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111733255</v>
+        <v>113071881</v>
       </c>
       <c r="B4" t="n">
-        <v>89081</v>
+        <v>88424</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4374</v>
+        <v>1008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulvaxing</t>
+          <t>Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrocybe chlorophana</t>
+          <t>Lycoperdon echinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Wünsche</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,14 +944,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundstorp Ö, Ög</t>
+          <t>Sundstorp, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549105</v>
+        <v>548974</v>
       </c>
       <c r="R4" t="n">
-        <v>6531857</v>
+        <v>6531870</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,12 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,16 +1010,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111733255</t>
+          <t>https://artportalen.se/Sighting/113071881</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111733276</v>
+        <v>111733255</v>
       </c>
       <c r="B5" t="n">
-        <v>89096</v>
+        <v>89081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4383</v>
+        <v>4374</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Småvaxing</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrocybe insipida</t>
+          <t>Hygrocybe chlorophana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(J.E.Lange) M.M.Moser</t>
+          <t>(Fr.) Wünsche</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1103,16 +1116,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111733276</t>
+          <t>https://artportalen.se/Sighting/111733255</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113071867</v>
+        <v>111733276</v>
       </c>
       <c r="B6" t="n">
-        <v>89106</v>
+        <v>89096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4394</v>
+        <v>4383</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Småvaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Hygrocybe insipida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(J.E.Lange) M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549118</v>
+        <v>549105</v>
       </c>
       <c r="R6" t="n">
-        <v>6531853</v>
+        <v>6531857</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,12 +1190,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,16 +1222,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113071867</t>
+          <t>https://artportalen.se/Sighting/111733276</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116982832</v>
+        <v>113071867</v>
       </c>
       <c r="B7" t="n">
-        <v>56830</v>
+        <v>89106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,46 +1239,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100092</v>
+        <v>4394</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundstorp, Hävla, Ög</t>
+          <t>Sundstorp Ö, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549012</v>
+        <v>549118</v>
       </c>
       <c r="R7" t="n">
-        <v>6531857</v>
+        <v>6531853</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1289,12 +1296,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,6 +1310,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1320,16 +1328,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116982832</t>
+          <t>https://artportalen.se/Sighting/113071867</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116982827</v>
+        <v>116982832</v>
       </c>
       <c r="B8" t="n">
-        <v>56835</v>
+        <v>56830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,21 +1345,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1431,38 +1439,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116982827</t>
+          <t>https://artportalen.se/Sighting/116982832</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116982834</v>
+        <v>116982827</v>
       </c>
       <c r="B9" t="n">
-        <v>56816</v>
+        <v>56835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1542,67 +1550,63 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116982834</t>
+          <t>https://artportalen.se/Sighting/116982827</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123873636</v>
+        <v>116982834</v>
       </c>
       <c r="B10" t="n">
-        <v>58815</v>
+        <v>56816</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208250</v>
+        <v>205998</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sundstorp, Ög</t>
+          <t>Sundstorp, Hävla, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548977</v>
+        <v>549012</v>
       </c>
       <c r="R10" t="n">
-        <v>6531892</v>
+        <v>6531857</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,12 +1630,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,16 +1644,10 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>Erik Zachariassen</t>
-        </is>
-      </c>
       <c r="AW10" t="inlineStr">
         <is>
           <t>Caspar Ström</t>
@@ -1663,16 +1661,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123873636</t>
+          <t>https://artportalen.se/Sighting/116982834</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126172122</v>
+        <v>123873636</v>
       </c>
       <c r="B11" t="n">
-        <v>99155</v>
+        <v>58815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,49 +1678,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223621</v>
+        <v>208250</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ängsstugorna, Hävla, Ög</t>
+          <t>Sundstorp, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548857</v>
+        <v>548977</v>
       </c>
       <c r="R11" t="n">
-        <v>6531511</v>
+        <v>6531892</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,12 +1745,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,6 +1764,11 @@
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>Erik Zachariassen</t>
+        </is>
+      </c>
       <c r="AW11" t="inlineStr">
         <is>
           <t>Caspar Ström</t>
@@ -1777,6 +1781,121 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123873636</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126172122</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ängsstugorna, Hävla, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>548857</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6531511</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126172122</t>
         </is>
@@ -1794,6 +1913,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31894-2022 artfynd.xlsx
+++ b/artfynd/A 31894-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135435136</v>
       </c>
       <c r="B3" t="n">
-        <v>107876</v>
+        <v>107878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31894-2022 artfynd.xlsx
+++ b/artfynd/A 31894-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135435136</v>
       </c>
       <c r="B3" t="n">
-        <v>107878</v>
+        <v>107901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
